--- a/uploads/TEMPLATE_IMPORT.xlsx
+++ b/uploads/TEMPLATE_IMPORT.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="20148" windowHeight="7044"/>
+    <workbookView windowWidth="21216" windowHeight="9660"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="16" uniqueCount="16">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="18" uniqueCount="18">
   <si>
     <t>epc</t>
   </si>
@@ -35,46 +35,52 @@
     <t>bib</t>
   </si>
   <si>
-    <t>E28011702000100587AA0B1B</t>
-  </si>
-  <si>
-    <t>E28011702000002587AA0B1B</t>
-  </si>
-  <si>
-    <t>E2801170200000B587AA0B1B</t>
-  </si>
-  <si>
-    <t>E28011702000128587A30B1B</t>
-  </si>
-  <si>
-    <t>E2801170200002A587A30B1B</t>
-  </si>
-  <si>
-    <t>E28011702000046587A50B1B</t>
-  </si>
-  <si>
-    <t>E28011702000043587A50B1B</t>
-  </si>
-  <si>
-    <t>E2801170200000D587AA0B1B</t>
-  </si>
-  <si>
-    <t>E28011702000029587A30B1B</t>
-  </si>
-  <si>
-    <t>E28011702000127587A30B1B</t>
-  </si>
-  <si>
-    <t>E28011702000045587A50B1B</t>
-  </si>
-  <si>
-    <t>E28011702000001587AA0B1B</t>
-  </si>
-  <si>
-    <t>E28011702000144587A50B1B</t>
-  </si>
-  <si>
-    <t>E2801170200000E587AA0B1B</t>
+    <t>E280699500007005E6C3DC68</t>
+  </si>
+  <si>
+    <t>E280699500006004DBB795AE</t>
+  </si>
+  <si>
+    <t>E280699500007004DBB791AE</t>
+  </si>
+  <si>
+    <t>E280699500007005E6C3E068</t>
+  </si>
+  <si>
+    <t>E280699500006005E6C3E468</t>
+  </si>
+  <si>
+    <t>E280699500006005E6C3D868</t>
+  </si>
+  <si>
+    <t>E280699500006005E6C3E868</t>
+  </si>
+  <si>
+    <t>E280699500006005E6C3F068</t>
+  </si>
+  <si>
+    <t>E280699500007005E6C3EC68</t>
+  </si>
+  <si>
+    <t>E2806915000040234BF42602</t>
+  </si>
+  <si>
+    <t>E2806915000050234BF0B203</t>
+  </si>
+  <si>
+    <t>E200470BD8D064261E82010E</t>
+  </si>
+  <si>
+    <t>E200470BDED064261EE2010A</t>
+  </si>
+  <si>
+    <t>E2002083980B02440500DF4E</t>
+  </si>
+  <si>
+    <t>E2005109670702241150A574</t>
+  </si>
+  <si>
+    <t>A123</t>
   </si>
 </sst>
 </file>
@@ -692,6 +698,9 @@
   </cellStyleXfs>
   <cellXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" quotePrefix="1">
       <alignment vertical="center"/>
     </xf>
   </cellXfs>
@@ -1227,7 +1236,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:B15"/>
+  <dimension ref="A1:B16"/>
   <sheetFormatPr defaultColWidth="8.88888888888889" defaultRowHeight="14.4" outlineLevelCol="1"/>
   <cols>
     <col min="1" max="1" width="28.4444444444444" customWidth="1"/>
@@ -1353,6 +1362,14 @@
         <v>4452</v>
       </c>
     </row>
+    <row r="16" spans="1:2">
+      <c r="A16" t="s">
+        <v>16</v>
+      </c>
+      <c r="B16" s="1" t="s">
+        <v>17</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <headerFooter/>
